--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Bullet.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Bullet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Id</t>
   </si>
   <si>
+    <t>#Desc</t>
+  </si>
+  <si>
     <t>Shape</t>
   </si>
   <si>
@@ -59,7 +62,16 @@
     <t>DestroyAction</t>
   </si>
   <si>
-    <t>Model</t>
+    <t>TargetNum</t>
+  </si>
+  <si>
+    <t>TickLimit</t>
+  </si>
+  <si>
+    <t>Tick1</t>
+  </si>
+  <si>
+    <t>Tick2</t>
   </si>
   <si>
     <t>##type</t>
@@ -68,18 +80,21 @@
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>(list#sep=,),string</t>
   </si>
   <si>
     <t>(list#sep=,),int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
+    <t>描述</t>
+  </si>
+  <si>
     <t>形状</t>
   </si>
   <si>
@@ -104,7 +119,25 @@
     <t>销毁前触发</t>
   </si>
   <si>
-    <t>模型</t>
+    <t>目标个数</t>
+  </si>
+  <si>
+    <t>结算次数限制</t>
+  </si>
+  <si>
+    <t>1档（0.5s）</t>
+  </si>
+  <si>
+    <t>1档（1s）</t>
+  </si>
+  <si>
+    <t>火球术子弹</t>
+  </si>
+  <si>
+    <t>虚空法球子弹</t>
+  </si>
+  <si>
+    <t>冲锋范围伤害</t>
   </si>
 </sst>
 </file>
@@ -739,8 +772,12 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1063,22 +1100,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="2" customWidth="1"/>
-    <col min="8" max="9" width="21.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.25" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="18.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
+    <col min="9" max="10" width="21.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.5" style="2" customWidth="1"/>
+    <col min="14" max="15" width="22.25" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,80 +1153,192 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:2">
+    <row r="4" s="2" customFormat="1" spans="2:15">
       <c r="B4" s="3">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2">
         <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H4" s="2">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>500</v>
+      </c>
+      <c r="H6" s="2">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7</v>
+      </c>
+      <c r="M6" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
